--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
@@ -2304,11 +2304,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10988156"/>
-        <c:axId val="23806990"/>
+        <c:axId val="42442163"/>
+        <c:axId val="35506455"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="10988156"/>
+        <c:axId val="42442163"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2342,7 +2342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23806990"/>
+        <c:crossAx val="35506455"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2354,7 +2354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="23806990"/>
+        <c:axId val="35506455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2397,7 +2397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10988156"/>
+        <c:crossAx val="42442163"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3370,11 +3370,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="533306"/>
-        <c:axId val="25262927"/>
+        <c:axId val="95679572"/>
+        <c:axId val="33354043"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="533306"/>
+        <c:axId val="95679572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3406,14 +3406,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25262927"/>
+        <c:crossAx val="33354043"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="25262927"/>
+        <c:axId val="33354043"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3486,7 +3486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533306"/>
+        <c:crossAx val="95679572"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2978,$B$3:$B$2978)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2978,$B$3:$B$2978)</f>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7733,7 +7733,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="S23" s="19" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -8284,23 +8284,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -12427,7 +12427,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18103,15 +18103,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="71" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>91.8329636612321</v>
+        <v>93.1495648469474</v>
       </c>
       <c r="F249" s="70" t="n">
         <v>46142</v>
@@ -18246,23 +18246,23 @@
       </c>
       <c r="T2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="H39" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="81"/>
       <c r="J39" s="81"/>
@@ -19651,7 +19651,7 @@
       <c r="P39" s="81"/>
       <c r="Q39" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
@@ -2304,11 +2304,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="42442163"/>
-        <c:axId val="35506455"/>
+        <c:axId val="5975190"/>
+        <c:axId val="76111232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="42442163"/>
+        <c:axId val="5975190"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2342,7 +2342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35506455"/>
+        <c:crossAx val="76111232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2354,7 +2354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="35506455"/>
+        <c:axId val="76111232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2397,7 +2397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42442163"/>
+        <c:crossAx val="5975190"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3370,11 +3370,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="95679572"/>
-        <c:axId val="33354043"/>
+        <c:axId val="37477566"/>
+        <c:axId val="29506737"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="95679572"/>
+        <c:axId val="37477566"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3406,14 +3406,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33354043"/>
+        <c:crossAx val="29506737"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="33354043"/>
+        <c:axId val="29506737"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3486,7 +3486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95679572"/>
+        <c:crossAx val="37477566"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
@@ -2304,11 +2304,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="5975190"/>
-        <c:axId val="76111232"/>
+        <c:axId val="16842313"/>
+        <c:axId val="83538320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="5975190"/>
+        <c:axId val="16842313"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2342,7 +2342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76111232"/>
+        <c:crossAx val="83538320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2354,7 +2354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="76111232"/>
+        <c:axId val="83538320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2397,7 +2397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5975190"/>
+        <c:crossAx val="16842313"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3370,11 +3370,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="37477566"/>
-        <c:axId val="29506737"/>
+        <c:axId val="5093036"/>
+        <c:axId val="273156"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="37477566"/>
+        <c:axId val="5093036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3406,14 +3406,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29506737"/>
+        <c:crossAx val="273156"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="29506737"/>
+        <c:axId val="273156"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3486,7 +3486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37477566"/>
+        <c:crossAx val="5093036"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_PLUS.xlsx
@@ -2304,11 +2304,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="16842313"/>
-        <c:axId val="83538320"/>
+        <c:axId val="89409352"/>
+        <c:axId val="36134721"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="16842313"/>
+        <c:axId val="89409352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2342,7 +2342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83538320"/>
+        <c:crossAx val="36134721"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2354,7 +2354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="83538320"/>
+        <c:axId val="36134721"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2397,7 +2397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16842313"/>
+        <c:crossAx val="89409352"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3370,11 +3370,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="5093036"/>
-        <c:axId val="273156"/>
+        <c:axId val="2914605"/>
+        <c:axId val="32650220"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="5093036"/>
+        <c:axId val="2914605"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3406,14 +3406,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="273156"/>
+        <c:crossAx val="32650220"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="273156"/>
+        <c:axId val="32650220"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3486,7 +3486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5093036"/>
+        <c:crossAx val="2914605"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
